--- a/base_colheita_atual.xlsx
+++ b/base_colheita_atual.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iago\Desktop\Projeto AFB Itapira - Automação de dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B966D59D-2EAC-4FEB-BFEC-AED2504695FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B73DC3D-06E7-49DD-A86F-49D6420EFA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -19931,7 +19944,7 @@
         <v>20.67</v>
       </c>
       <c r="J729">
-        <v>151.1</v>
+        <v>75.55</v>
       </c>
       <c r="K729">
         <v>1561.6185</v>
@@ -20087,7 +20100,7 @@
         <v>10.25</v>
       </c>
       <c r="J735">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="K735">
         <v>666.25</v>
@@ -20113,7 +20126,7 @@
         <v>9.629999999999999</v>
       </c>
       <c r="J736">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="K736">
         <v>625.95000000000005</v>
@@ -20139,7 +20152,7 @@
         <v>4.25</v>
       </c>
       <c r="J737">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="K737">
         <v>267.75</v>
@@ -20165,7 +20178,7 @@
         <v>13</v>
       </c>
       <c r="J738">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="K738">
         <v>819</v>
@@ -20191,7 +20204,7 @@
         <v>5.08</v>
       </c>
       <c r="J739">
-        <v>129.08000000000001</v>
+        <v>64.540000000000006</v>
       </c>
       <c r="K739">
         <v>327.86320000000001</v>
@@ -20217,7 +20230,7 @@
         <v>12.92</v>
       </c>
       <c r="J740">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="K740">
         <v>801.04</v>
@@ -20424,6 +20437,9 @@
       <c r="I748">
         <v>0</v>
       </c>
+      <c r="J748">
+        <v>0</v>
+      </c>
       <c r="K748">
         <v>0</v>
       </c>
@@ -20447,6 +20463,9 @@
       <c r="I749">
         <v>0</v>
       </c>
+      <c r="J749">
+        <v>0</v>
+      </c>
       <c r="K749">
         <v>0</v>
       </c>
@@ -21040,6 +21059,9 @@
         <v>1</v>
       </c>
       <c r="I772">
+        <v>0</v>
+      </c>
+      <c r="J772">
         <v>0</v>
       </c>
       <c r="K772">

--- a/base_colheita_atual.xlsx
+++ b/base_colheita_atual.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iago\Desktop\Projeto AFB Itapira - Automação de dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD817A58-21D3-4259-BF49-91B1B453FDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9C533E-9A3E-44DB-B121-F46429556060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="1" r:id="rId1"/>
     <sheet name="Mudas" sheetId="2" r:id="rId2"/>
     <sheet name="Reforma" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dados!$A$1:$K$787</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -20468,13 +20471,13 @@
         <v>1</v>
       </c>
       <c r="I748">
-        <v>0</v>
+        <v>39.880000000000003</v>
       </c>
       <c r="J748">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="K748">
-        <v>0</v>
+        <v>3110.64</v>
       </c>
     </row>
     <row r="749" spans="1:11" x14ac:dyDescent="0.3">
@@ -20494,13 +20497,13 @@
         <v>5</v>
       </c>
       <c r="I749">
-        <v>0</v>
+        <v>34.229999999999997</v>
       </c>
       <c r="J749">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K749">
-        <v>0</v>
+        <v>2396.1</v>
       </c>
     </row>
     <row r="750" spans="1:11" x14ac:dyDescent="0.3">
@@ -20913,7 +20916,7 @@
         <v>20.76</v>
       </c>
       <c r="J765">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="K765">
         <v>1079.52</v>
@@ -21092,13 +21095,13 @@
         <v>1</v>
       </c>
       <c r="I772">
-        <v>0</v>
+        <v>14.49</v>
       </c>
       <c r="J772">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K772">
-        <v>0</v>
+        <v>1680.8354999999999</v>
       </c>
     </row>
     <row r="773" spans="1:11" x14ac:dyDescent="0.3">

--- a/base_colheita_atual.xlsx
+++ b/base_colheita_atual.xlsx
@@ -18275,7 +18275,7 @@
       </c>
       <c r="E604" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="F604" t="n">
